--- a/base_de_dados.xlsx
+++ b/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Dropbox\DROP BOX RICARDO\ORÇAMENTOMODELO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E77CF69-8BAF-4D8B-B276-2D19133B0CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{4E77CF69-8BAF-4D8B-B276-2D19133B0CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91C5EF1E-DF9F-40DC-BF12-C698C9128A1F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -723,6 +723,7 @@
         <v>10.54</v>
       </c>
       <c r="AB2" s="3">
+        <f>58.39</f>
         <v>58.39</v>
       </c>
     </row>
@@ -798,7 +799,8 @@
         <v>3.01125</v>
       </c>
       <c r="AB3" s="3">
-        <v>47.82</v>
+        <f>38.2530539*1.25</f>
+        <v>47.816317374999997</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="30.75">
@@ -873,7 +875,8 @@
         <v>5.346000000000001</v>
       </c>
       <c r="AB4" s="3">
-        <v>34.630000000000003</v>
+        <f>30.59*1.25</f>
+        <v>38.237499999999997</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="30.75">
@@ -948,7 +951,8 @@
         <v>3.2120000000000002</v>
       </c>
       <c r="AB5" s="3">
-        <v>38.229999999999997</v>
+        <f>27.7072716*1.25</f>
+        <v>34.634089500000002</v>
       </c>
     </row>
   </sheetData>
